--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_10/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_10/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>60.12</v>
+        <v>60.09</v>
       </c>
       <c r="D2" t="n">
-        <v>21.51</v>
+        <v>20.78</v>
       </c>
       <c r="E2" t="n">
-        <v>35.77</v>
+        <v>34.58</v>
       </c>
       <c r="F2" t="n">
-        <v>34.84</v>
+        <v>36.47</v>
       </c>
       <c r="G2" t="n">
-        <v>40.64</v>
+        <v>41.83</v>
       </c>
       <c r="H2" t="n">
-        <v>55.35</v>
+        <v>53.67</v>
       </c>
       <c r="I2" t="n">
-        <v>77.47</v>
+        <v>76.63</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>65.16</v>
+        <v>63.53</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>40.9</v>
+        <v>45.96</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1</v>
+        <v>0.59</v>
       </c>
       <c r="E3" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="F3" t="n">
-        <v>38.96</v>
+        <v>45.64</v>
       </c>
       <c r="G3" t="n">
-        <v>40.49</v>
+        <v>45.65</v>
       </c>
       <c r="H3" t="n">
-        <v>40.77</v>
+        <v>45.7</v>
       </c>
       <c r="I3" t="n">
-        <v>40.79</v>
+        <v>45.92</v>
       </c>
       <c r="J3" t="n">
-        <v>47.25</v>
+        <v>48.02</v>
       </c>
       <c r="K3" t="n">
-        <v>8.279999999999999</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.63</v>
+        <v>7.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="E4" t="n">
-        <v>16.48</v>
+        <v>15.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.47</v>
+        <v>5.68</v>
       </c>
       <c r="G4" t="n">
         <v>6.81</v>
       </c>
       <c r="H4" t="n">
-        <v>7.36</v>
+        <v>7.04</v>
       </c>
       <c r="I4" t="n">
-        <v>8.43</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>9.99</v>
+        <v>9.67</v>
       </c>
       <c r="K4" t="n">
-        <v>4.52</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>108.27</v>
+        <v>114.33</v>
       </c>
       <c r="D5" t="n">
-        <v>12.89</v>
+        <v>11.92</v>
       </c>
       <c r="E5" t="n">
-        <v>11.91</v>
+        <v>10.43</v>
       </c>
       <c r="F5" t="n">
-        <v>83.62</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>103.69</v>
+        <v>110.74</v>
       </c>
       <c r="H5" t="n">
-        <v>106.91</v>
+        <v>118.98</v>
       </c>
       <c r="I5" t="n">
-        <v>115.4</v>
+        <v>120.64</v>
       </c>
       <c r="J5" t="n">
-        <v>141.96</v>
+        <v>146.15</v>
       </c>
       <c r="K5" t="n">
-        <v>58.34</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.53</v>
+        <v>4.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>6.77</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>4.09</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4.37</v>
       </c>
       <c r="I6" t="n">
-        <v>3.67</v>
+        <v>4.63</v>
       </c>
       <c r="J6" t="n">
-        <v>4.44</v>
+        <v>4.88</v>
       </c>
       <c r="K6" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>
